--- a/samples/sample1.xlsx
+++ b/samples/sample1.xlsx
@@ -38,11 +38,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -62,12 +63,23 @@
     <font>
       <sz val="11"/>
       <name val="Meiryo UI"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Noto Serif JP"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Noto Serif JP"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Meiryo UI"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -83,12 +95,33 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -117,13 +150,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -149,9 +190,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>270360</xdr:colOff>
+      <xdr:colOff>270000</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>52920</xdr:rowOff>
+      <xdr:rowOff>52560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -160,8 +201,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4089600" y="1243440"/>
-          <a:ext cx="2151000" cy="760320"/>
+          <a:off x="4082040" y="1243440"/>
+          <a:ext cx="2146680" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -186,7 +227,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -195,8 +240,7 @@
             <a:t>作業した記録から作業報告書を作成</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -212,9 +256,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>37080</xdr:colOff>
+      <xdr:colOff>36720</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>114120</xdr:rowOff>
+      <xdr:rowOff>113760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -223,8 +267,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5756760" y="1805400"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="5747400" y="1805400"/>
+          <a:ext cx="1241280" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -283,9 +327,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>425520</xdr:colOff>
+      <xdr:colOff>425160</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>59040</xdr:rowOff>
+      <xdr:rowOff>58680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -294,8 +338,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2020320" y="1455840"/>
-          <a:ext cx="395280" cy="391320"/>
+          <a:off x="2016360" y="1455840"/>
+          <a:ext cx="394920" cy="390960"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -321,7 +365,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Noto Serif JP"/>
@@ -356,8 +404,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2416320" y="1647720"/>
-          <a:ext cx="1671120" cy="0"/>
+          <a:off x="2412360" y="1647720"/>
+          <a:ext cx="1667520" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -388,9 +436,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>826920</xdr:colOff>
+      <xdr:colOff>826560</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>99360</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -399,8 +447,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3561480" y="1790640"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="3555720" y="1790640"/>
+          <a:ext cx="1243440" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -459,9 +507,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>888840</xdr:colOff>
+      <xdr:colOff>888480</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>62640</xdr:rowOff>
+      <xdr:rowOff>62280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -470,8 +518,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7693200" y="1253160"/>
-          <a:ext cx="2151000" cy="760320"/>
+          <a:off x="7679880" y="1253160"/>
+          <a:ext cx="2147040" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -496,7 +544,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -519,8 +571,7 @@
             <a:t>部門に提出</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -547,8 +598,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6226920" y="1625760"/>
-          <a:ext cx="1478520" cy="0"/>
+          <a:off x="6215400" y="1625760"/>
+          <a:ext cx="1476720" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -579,9 +630,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>579960</xdr:colOff>
+      <xdr:colOff>579600</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>105840</xdr:rowOff>
+      <xdr:rowOff>105480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -590,8 +641,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9284760" y="1797120"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="9267840" y="1797120"/>
+          <a:ext cx="1243080" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -650,9 +701,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>864000</xdr:colOff>
+      <xdr:colOff>863640</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>144000</xdr:rowOff>
+      <xdr:rowOff>143640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -661,8 +712,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11648520" y="6048720"/>
-          <a:ext cx="2151000" cy="760320"/>
+          <a:off x="11627640" y="6048720"/>
+          <a:ext cx="2146680" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -687,7 +738,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -696,12 +751,15 @@
             <a:t>受け取った作業報告書を</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
+            <a:latin typeface="Noto Serif JP"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -710,8 +768,7 @@
             <a:t>スキャンして電子化</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -738,8 +795,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9795600" y="1634040"/>
-          <a:ext cx="1848960" cy="4770720"/>
+          <a:off x="9778680" y="1634040"/>
+          <a:ext cx="1845000" cy="4770720"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -770,9 +827,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>87120</xdr:colOff>
+      <xdr:colOff>86760</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>134640</xdr:rowOff>
+      <xdr:rowOff>134280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -781,8 +838,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10782000" y="6540120"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="10762920" y="6540120"/>
+          <a:ext cx="1241640" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -841,9 +898,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>681840</xdr:colOff>
+      <xdr:colOff>681480</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>9720</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -852,8 +909,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13366800" y="6577920"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="13341960" y="6577920"/>
+          <a:ext cx="1243440" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -926,9 +983,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>270360</xdr:colOff>
+      <xdr:colOff>270000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>158400</xdr:rowOff>
+      <xdr:rowOff>158040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -937,8 +994,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4089600" y="3787200"/>
-          <a:ext cx="2151000" cy="760320"/>
+          <a:off x="4082040" y="3787200"/>
+          <a:ext cx="2146680" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -963,7 +1020,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -972,8 +1033,7 @@
             <a:t>作業した記録から作業報告書を作成</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -989,9 +1049,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>37080</xdr:colOff>
+      <xdr:colOff>36720</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>56880</xdr:rowOff>
+      <xdr:rowOff>56520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1000,8 +1060,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5756760" y="4349160"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="5747400" y="4349160"/>
+          <a:ext cx="1241280" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -1060,9 +1120,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>425520</xdr:colOff>
+      <xdr:colOff>425160</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>1800</xdr:rowOff>
+      <xdr:rowOff>1440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1071,8 +1131,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2020320" y="3999600"/>
-          <a:ext cx="395280" cy="391320"/>
+          <a:off x="2016360" y="3999600"/>
+          <a:ext cx="394920" cy="390960"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1098,7 +1158,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Noto Serif JP"/>
@@ -1133,8 +1197,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2416320" y="4191480"/>
-          <a:ext cx="1671120" cy="0"/>
+          <a:off x="2412360" y="4191480"/>
+          <a:ext cx="1667520" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1165,9 +1229,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>826920</xdr:colOff>
+      <xdr:colOff>826560</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>42120</xdr:rowOff>
+      <xdr:rowOff>41760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1176,8 +1240,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3561480" y="4334400"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="3555720" y="4334400"/>
+          <a:ext cx="1243440" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -1236,9 +1300,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>888840</xdr:colOff>
+      <xdr:colOff>888480</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>5400</xdr:rowOff>
+      <xdr:rowOff>5040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1247,8 +1311,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7693200" y="3796920"/>
-          <a:ext cx="2151000" cy="760320"/>
+          <a:off x="7679880" y="3796920"/>
+          <a:ext cx="2147040" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1273,7 +1337,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -1296,8 +1364,7 @@
             <a:t>部門に提出</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -1324,8 +1391,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6226920" y="4169520"/>
-          <a:ext cx="1478520" cy="0"/>
+          <a:off x="6215400" y="4169520"/>
+          <a:ext cx="1476720" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1356,9 +1423,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>579960</xdr:colOff>
+      <xdr:colOff>579600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>48600</xdr:rowOff>
+      <xdr:rowOff>48240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1367,8 +1434,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9284760" y="4340880"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="9267840" y="4340880"/>
+          <a:ext cx="1243080" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -1438,8 +1505,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9825480" y="4120200"/>
-          <a:ext cx="1760400" cy="2286720"/>
+          <a:off x="9808560" y="4120200"/>
+          <a:ext cx="1756440" cy="2286720"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1470,9 +1537,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>541800</xdr:colOff>
+      <xdr:colOff>541440</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>14760</xdr:rowOff>
+      <xdr:rowOff>14400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1481,8 +1548,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15980040" y="6081840"/>
-          <a:ext cx="2472480" cy="760320"/>
+          <a:off x="15949800" y="6081840"/>
+          <a:ext cx="2468160" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1507,7 +1574,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -1516,12 +1587,15 @@
             <a:t>スキャンして電子化した</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
+            <a:latin typeface="Noto Serif JP"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -1544,12 +1618,15 @@
             <a:t>に配置</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
+            <a:latin typeface="Noto Serif JP"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -1572,8 +1649,7 @@
             <a:t>に登録</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -1600,8 +1676,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13812840" y="6397560"/>
-          <a:ext cx="2235960" cy="9360"/>
+          <a:off x="13788000" y="6397560"/>
+          <a:ext cx="2230560" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1632,9 +1708,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>931680</xdr:colOff>
+      <xdr:colOff>931320</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>32400</xdr:rowOff>
+      <xdr:rowOff>32040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1643,8 +1719,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17596800" y="6762960"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="17564400" y="6762960"/>
+          <a:ext cx="1243440" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -1703,9 +1779,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>474480</xdr:colOff>
+      <xdr:colOff>474120</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>120240</xdr:rowOff>
+      <xdr:rowOff>119880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1714,8 +1790,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13159440" y="6850800"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="13134600" y="6850800"/>
+          <a:ext cx="1243440" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -1774,9 +1850,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>672840</xdr:colOff>
+      <xdr:colOff>672480</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>131040</xdr:rowOff>
+      <xdr:rowOff>130680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1785,8 +1861,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15347880" y="6699240"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="15319440" y="6699240"/>
+          <a:ext cx="1243440" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -1859,9 +1935,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>524880</xdr:colOff>
+      <xdr:colOff>524520</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>135000</xdr:rowOff>
+      <xdr:rowOff>134640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1870,8 +1946,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15199920" y="7028280"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="15171480" y="7028280"/>
+          <a:ext cx="1243440" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -1930,9 +2006,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>243720</xdr:colOff>
+      <xdr:colOff>243360</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>25920</xdr:rowOff>
+      <xdr:rowOff>25560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1941,8 +2017,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19662120" y="6093000"/>
-          <a:ext cx="2472480" cy="760320"/>
+          <a:off x="19626120" y="6093000"/>
+          <a:ext cx="2466360" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1967,7 +2043,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -1976,12 +2056,15 @@
             <a:t>報告書をシュレッダーに</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
+            <a:latin typeface="Noto Serif JP"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -1990,8 +2073,7 @@
             <a:t>かけて廃棄</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2018,8 +2100,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18350640" y="6440760"/>
-          <a:ext cx="1382760" cy="52200"/>
+          <a:off x="18316440" y="6440760"/>
+          <a:ext cx="1380960" cy="52200"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2050,9 +2132,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>590040</xdr:colOff>
+      <xdr:colOff>589680</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>17640</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2061,8 +2143,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19245240" y="6748200"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="19209240" y="6748200"/>
+          <a:ext cx="1243080" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -2121,9 +2203,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>851760</xdr:colOff>
+      <xdr:colOff>851400</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>97920</xdr:rowOff>
+      <xdr:rowOff>97560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2132,8 +2214,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16680960" y="10610280"/>
-          <a:ext cx="1086480" cy="704160"/>
+          <a:off x="16650720" y="10610280"/>
+          <a:ext cx="1083960" cy="703800"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartMagneticDisk">
           <a:avLst/>
@@ -2158,7 +2240,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Noto Serif JP"/>
@@ -2170,7 +2256,11 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Noto Serif JP"/>
@@ -2211,7 +2301,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="17174160" y="6827400"/>
+          <a:off x="17141760" y="6827400"/>
           <a:ext cx="46800" cy="3807000"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -2237,15 +2327,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>941760</xdr:colOff>
+      <xdr:colOff>358920</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>119880</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>342000</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>23760</xdr:rowOff>
+      <xdr:rowOff>95400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>751680</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>161280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2254,8 +2344,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="34773120" y="3533760"/>
-          <a:ext cx="395280" cy="391320"/>
+          <a:off x="34125840" y="3509280"/>
+          <a:ext cx="392760" cy="390960"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2281,7 +2371,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Noto Serif JP"/>
@@ -2305,9 +2399,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>695880</xdr:colOff>
+      <xdr:colOff>695520</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>82080</xdr:rowOff>
+      <xdr:rowOff>81720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2316,8 +2410,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18515160" y="10594440"/>
-          <a:ext cx="1086480" cy="704160"/>
+          <a:off x="18480960" y="10594440"/>
+          <a:ext cx="1084320" cy="703800"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartMagneticDisk">
           <a:avLst/>
@@ -2342,7 +2436,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Noto Serif JP"/>
@@ -2354,7 +2452,11 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Noto Serif JP"/>
@@ -2395,8 +2497,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17226000" y="6827400"/>
-          <a:ext cx="1847880" cy="3752640"/>
+          <a:off x="17193600" y="6827400"/>
+          <a:ext cx="1844280" cy="3752640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2427,9 +2529,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>906840</xdr:colOff>
+      <xdr:colOff>906480</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>9720</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2438,8 +2540,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23310360" y="6076800"/>
-          <a:ext cx="2472480" cy="760320"/>
+          <a:off x="23266800" y="6076800"/>
+          <a:ext cx="2468160" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2464,7 +2566,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -2473,12 +2579,15 @@
             <a:t>電子化された報告書から</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
+            <a:latin typeface="Noto Serif JP"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -2487,8 +2596,7 @@
             <a:t>データを抽出して改善案ファイルの生成</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2504,9 +2612,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>252360</xdr:colOff>
+      <xdr:colOff>252000</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>134640</xdr:rowOff>
+      <xdr:rowOff>134280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2515,8 +2623,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16917480" y="10116720"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="16885080" y="10116720"/>
+          <a:ext cx="1243440" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -2600,8 +2708,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21943440" y="6449760"/>
-          <a:ext cx="1382760" cy="52200"/>
+          <a:off x="21901680" y="6449760"/>
+          <a:ext cx="1380960" cy="52200"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2632,9 +2740,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>722160</xdr:colOff>
+      <xdr:colOff>721800</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>8280</xdr:rowOff>
+      <xdr:rowOff>7920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2643,8 +2751,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25347600" y="6576480"/>
-          <a:ext cx="1245600" cy="421920"/>
+          <a:off x="25300080" y="6576480"/>
+          <a:ext cx="1243440" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="foldedCorner">
           <a:avLst>
@@ -2728,8 +2836,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25761600" y="6392880"/>
-          <a:ext cx="1382760" cy="52200"/>
+          <a:off x="25714080" y="6392880"/>
+          <a:ext cx="1379160" cy="52200"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2760,9 +2868,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>702000</xdr:colOff>
+      <xdr:colOff>701640</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2771,8 +2879,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27085680" y="6048000"/>
-          <a:ext cx="2472480" cy="760320"/>
+          <a:off x="27034560" y="6048000"/>
+          <a:ext cx="2468160" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2797,7 +2905,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -2806,8 +2918,7 @@
             <a:t>各部門に配布</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2823,9 +2934,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>440640</xdr:colOff>
+      <xdr:colOff>440280</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>8280</xdr:rowOff>
+      <xdr:rowOff>7920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2834,8 +2945,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="30804480" y="1361160"/>
-          <a:ext cx="2472480" cy="760320"/>
+          <a:off x="30747600" y="1361160"/>
+          <a:ext cx="2466360" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2860,7 +2971,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -2869,8 +2984,7 @@
             <a:t>改善案ファイルを受け取る</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2886,9 +3000,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>518400</xdr:colOff>
+      <xdr:colOff>518040</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>75600</xdr:rowOff>
+      <xdr:rowOff>75240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2897,8 +3011,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="30882240" y="3379320"/>
-          <a:ext cx="2472480" cy="760320"/>
+          <a:off x="30823200" y="3379320"/>
+          <a:ext cx="2468520" cy="759960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2923,7 +3037,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
               <a:latin typeface="Meiryo UI"/>
@@ -2932,8 +3050,7 @@
             <a:t>改善案ファイルを受け取る</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="Meiryo UI"/>
-            <a:ea typeface="Meiryo UI"/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2960,8 +3077,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="29561040" y="1801800"/>
-          <a:ext cx="1233360" cy="4523400"/>
+          <a:off x="29505960" y="1801800"/>
+          <a:ext cx="1231560" cy="4523400"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3003,8 +3120,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="29553840" y="3765960"/>
-          <a:ext cx="1253520" cy="2628360"/>
+          <a:off x="29498760" y="3765960"/>
+          <a:ext cx="1251720" cy="2628360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3046,8 +3163,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="33246000" y="1663920"/>
-          <a:ext cx="1570680" cy="9360"/>
+          <a:off x="33183360" y="1663920"/>
+          <a:ext cx="1568880" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3073,14 +3190,14 @@
     <xdr:from>
       <xdr:col>33</xdr:col>
       <xdr:colOff>517320</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>153000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>916920</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>28440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>385560</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>40680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3088,9 +3205,9 @@
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="33353640" y="3729240"/>
-          <a:ext cx="1394640" cy="38160"/>
+        <a:xfrm>
+          <a:off x="33291000" y="3767400"/>
+          <a:ext cx="861480" cy="12240"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3114,16 +3231,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>990720</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>158400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>390960</xdr:colOff>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>342720</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>85320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>735480</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>61920</xdr:rowOff>
+      <xdr:rowOff>151200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3132,8 +3249,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="34822080" y="1458720"/>
-          <a:ext cx="395280" cy="391320"/>
+          <a:off x="43047720" y="1548360"/>
+          <a:ext cx="392760" cy="390960"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3159,7 +3276,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Noto Serif JP"/>
@@ -3194,8 +3315,564 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="19145880" y="6792480"/>
-          <a:ext cx="5490000" cy="3750840"/>
+          <a:off x="19109880" y="6792480"/>
+          <a:ext cx="5480280" cy="3750840"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="36000">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:tailEnd len="med" type="triangle" w="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>820440</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>138240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>237960</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>97920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="シェイプ 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="34587360" y="1276200"/>
+          <a:ext cx="3389760" cy="772560"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="ffffff"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="0" rIns="0" tIns="0" bIns="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr b="0" lang="ja-JP" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Noto Serif JP"/>
+              <a:ea typeface="Meiryo UI"/>
+            </a:rPr>
+            <a:t>改善ファイルが実行可能か</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
+            <a:latin typeface="Noto Serif JP"/>
+            <a:ea typeface="Meiryo UI"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>509040</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>121680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>196920</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>89640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="線 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="36262080" y="2072520"/>
+          <a:ext cx="1674000" cy="1268280"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="36000">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:tailEnd len="med" type="triangle" w="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>254160</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>15840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>615600</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>89280</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="線 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="37993320" y="1641600"/>
+          <a:ext cx="1354680" cy="73440"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="36000">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:tailEnd len="med" type="triangle" w="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>230040</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>32760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>533520</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>105840</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="テキスト枠 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="37969200" y="1333080"/>
+          <a:ext cx="303480" cy="235800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" rIns="0" tIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:r>
+            <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+              <a:latin typeface="Noto Serif JP"/>
+            </a:rPr>
+            <a:t>Yes</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+            <a:latin typeface="Noto Serif JP"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>451800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>56880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>755280</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>130320</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="テキスト枠 2"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="36204840" y="2332800"/>
+          <a:ext cx="303480" cy="235800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" rIns="0" tIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:r>
+            <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+              <a:latin typeface="Noto Serif JP"/>
+            </a:rPr>
+            <a:t>No</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+            <a:latin typeface="Noto Serif JP"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>224640</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>120240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>706680</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>67320</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="シェイプ 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="37963800" y="3046320"/>
+          <a:ext cx="2468520" cy="759960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="ffffff"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="0" rIns="0" tIns="0" bIns="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+              <a:latin typeface="Meiryo UI"/>
+              <a:ea typeface="Meiryo UI"/>
+            </a:rPr>
+            <a:t>改善案を無視する</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:latin typeface="Noto Serif JP"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>594000</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>39240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>83160</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>148680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="シェイプ 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="39326400" y="1339560"/>
+          <a:ext cx="2468520" cy="759960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="ffffff"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="0" rIns="0" tIns="0" bIns="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+              <a:latin typeface="Meiryo UI"/>
+              <a:ea typeface="Meiryo UI"/>
+            </a:rPr>
+            <a:t>改善案を実行する</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:latin typeface="Noto Serif JP"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>57600</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>97200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>419040</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>8280</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="線 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="41769360" y="1722960"/>
+          <a:ext cx="1354680" cy="73440"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="36000">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:tailEnd len="med" type="triangle" w="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>39240</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>101520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>432000</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>5040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="シェイプ 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="41751000" y="3190320"/>
+          <a:ext cx="392760" cy="390960"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="ffffff"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:tailEnd len="med" type="triangle" w="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="0" rIns="0" tIns="0" bIns="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="ja-JP" sz="1200" spc="-1" strike="noStrike">
+              <a:latin typeface="Noto Serif JP"/>
+            </a:rPr>
+            <a:t>終了</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+            <a:latin typeface="Noto Serif JP"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>747000</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>113760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>115560</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>24480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="線 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="40472640" y="3364920"/>
+          <a:ext cx="1354680" cy="73440"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3226,9 +3903,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A6:A50"/>
-  <sheetFormatPr defaultColWidth="15.0703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.04296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -3263,10 +3940,10 @@
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
@@ -3313,10 +3990,10 @@
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1"/>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1"/>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>2</v>
       </c>
@@ -3366,7 +4043,7 @@
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1"/>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1"/>
     </row>
   </sheetData>
